--- a/ksoft_old/docs/records/Finance_Modality_Enum.xlsx
+++ b/ksoft_old/docs/records/Finance_Modality_Enum.xlsx
@@ -1367,13 +1367,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBBC2083-339E-4312-AC5F-17AE92B11735}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69381DAB-2EDD-4302-9416-FCA5D6F5A795}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD1C2889-8EE0-4234-9849-BC3580C18676}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9141D1FE-9E31-4090-B35F-4A57F0D3C233}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BAC5158-7CC8-4E30-9644-F5EFC39C4F6C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DD98493-F3A4-480B-B631-C12EEC82702E}"/>
 </file>
--- a/ksoft_old/docs/records/Finance_Modality_Enum.xlsx
+++ b/ksoft_old/docs/records/Finance_Modality_Enum.xlsx
@@ -1367,13 +1367,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69381DAB-2EDD-4302-9416-FCA5D6F5A795}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC455BE5-601B-4116-8F38-4E5B76777B5A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9141D1FE-9E31-4090-B35F-4A57F0D3C233}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6964A69D-416D-4BEC-B548-895E9213F04F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DD98493-F3A4-480B-B631-C12EEC82702E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4215BF42-33F8-4AC0-BC0E-3EF36F8D5AB3}"/>
 </file>
--- a/ksoft_old/docs/records/Finance_Modality_Enum.xlsx
+++ b/ksoft_old/docs/records/Finance_Modality_Enum.xlsx
@@ -1367,13 +1367,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC455BE5-601B-4116-8F38-4E5B76777B5A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBBC2083-339E-4312-AC5F-17AE92B11735}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6964A69D-416D-4BEC-B548-895E9213F04F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD1C2889-8EE0-4234-9849-BC3580C18676}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4215BF42-33F8-4AC0-BC0E-3EF36F8D5AB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BAC5158-7CC8-4E30-9644-F5EFC39C4F6C}"/>
 </file>